--- a/data/trans_dic/P79A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P79A_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,23</t>
+          <t>0,48; 2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,0</t>
+          <t>0,91; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,72</t>
+          <t>0,82; 2,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,05</t>
+          <t>1,22; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,19</t>
+          <t>1,08; 3,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,53</t>
+          <t>1,37; 2,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,82</t>
+          <t>2,08; 6,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,63</t>
+          <t>1,13; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,8</t>
+          <t>1,95; 4,06</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,43</t>
+          <t>1,7; 3,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,17</t>
+          <t>2,42; 4,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,56</t>
+          <t>2,31; 3,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,77</t>
+          <t>1,88; 3,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,58</t>
+          <t>1,81; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,52</t>
+          <t>1,94; 2,78</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>19317</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2746; 14159</t>
+          <t>3348; 14870</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4561; 14531</t>
+          <t>6697; 21375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9177; 23463</t>
+          <t>11678; 30153</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>42287</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7678; 36390</t>
+          <t>12833; 40197</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10250; 30586</t>
+          <t>11590; 33652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22290; 54539</t>
+          <t>28998; 61183</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>28983</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>44101</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14380; 40996</t>
+          <t>16670; 49006</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5969; 33870</t>
+          <t>9203; 26974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24488; 62280</t>
+          <t>31565; 65661</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>63936</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13643; 31753</t>
+          <t>16811; 37342</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21752; 45705</t>
+          <t>27056; 51853</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41598; 72048</t>
+          <t>48644; 81225</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>85362</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74199</t>
+          <t>84279</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145352</t>
+          <t>169641</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51781; 95956</t>
+          <t>66461; 111769</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54238; 95737</t>
+          <t>67586; 106853</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115676; 180662</t>
+          <t>141286; 202044</t>
         </is>
       </c>
     </row>
